--- a/NMA_data_analysis_subset_RationalNumbers.xlsx
+++ b/NMA_data_analysis_subset_RationalNumbers.xlsx
@@ -1404,10 +1404,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN2">
+        <v>3</v>
       </c>
       <c r="AO2">
         <v>73</v>
@@ -1558,19 +1556,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM2">
+        <v>0</v>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU2">
@@ -1579,11 +1570,6 @@
       <c r="EW2">
         <v>2</v>
       </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY2">
         <v>4</v>
       </c>
@@ -1602,10 +1588,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE2">
+        <v>1</v>
       </c>
       <c r="FF2" t="inlineStr">
         <is>
@@ -1617,17 +1601,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH2">
+        <v>1</v>
       </c>
       <c r="FL2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1786,10 +1763,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN3">
+        <v>3</v>
       </c>
       <c r="AO3">
         <v>73</v>
@@ -1940,19 +1915,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM3">
+        <v>0</v>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ3" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU3">
@@ -1961,11 +1929,6 @@
       <c r="EW3">
         <v>2</v>
       </c>
-      <c r="EX3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY3">
         <v>4</v>
       </c>
@@ -1979,10 +1942,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE3">
+        <v>1</v>
       </c>
       <c r="FF3" t="inlineStr">
         <is>
@@ -1994,17 +1955,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH3">
+        <v>1</v>
       </c>
       <c r="FL3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2163,10 +2117,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN4">
+        <v>3</v>
       </c>
       <c r="AO4">
         <v>73</v>
@@ -2317,19 +2269,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM4">
+        <v>0</v>
       </c>
       <c r="EN4" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ4" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU4">
@@ -2338,11 +2283,6 @@
       <c r="EW4">
         <v>2</v>
       </c>
-      <c r="EX4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY4">
         <v>4</v>
       </c>
@@ -2361,10 +2301,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE4">
+        <v>1</v>
       </c>
       <c r="FF4" t="inlineStr">
         <is>
@@ -2376,17 +2314,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH4">
+        <v>1</v>
       </c>
       <c r="FL4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2545,10 +2476,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN5">
+        <v>3</v>
       </c>
       <c r="AO5">
         <v>73</v>
@@ -2699,19 +2628,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM5">
+        <v>0</v>
       </c>
       <c r="EN5" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ5" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU5">
@@ -2720,11 +2642,6 @@
       <c r="EW5">
         <v>2</v>
       </c>
-      <c r="EX5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY5">
         <v>4</v>
       </c>
@@ -2743,10 +2660,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE5">
+        <v>1</v>
       </c>
       <c r="FF5" t="inlineStr">
         <is>
@@ -2758,17 +2673,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH5">
+        <v>1</v>
       </c>
       <c r="FL5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2927,10 +2835,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN6">
+        <v>3</v>
       </c>
       <c r="AO6">
         <v>73</v>
@@ -3081,19 +2987,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM6">
+        <v>0</v>
       </c>
       <c r="EN6" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ6" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU6">
@@ -3102,11 +3001,6 @@
       <c r="EW6">
         <v>2</v>
       </c>
-      <c r="EX6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY6">
         <v>4</v>
       </c>
@@ -3125,10 +3019,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE6">
+        <v>1</v>
       </c>
       <c r="FF6" t="inlineStr">
         <is>
@@ -3140,17 +3032,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH6">
+        <v>1</v>
       </c>
       <c r="FL6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3319,10 +3204,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN7">
+        <v>3</v>
       </c>
       <c r="AO7">
         <v>73</v>
@@ -3478,19 +3361,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM7">
+        <v>0</v>
       </c>
       <c r="EN7" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ7" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU7">
@@ -3499,11 +3375,6 @@
       <c r="EW7">
         <v>2</v>
       </c>
-      <c r="EX7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY7">
         <v>4</v>
       </c>
@@ -3522,10 +3393,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE7">
+        <v>1</v>
       </c>
       <c r="FF7" t="inlineStr">
         <is>
@@ -3537,17 +3406,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH7">
+        <v>1</v>
       </c>
       <c r="FL7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3711,10 +3573,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN8">
+        <v>3</v>
       </c>
       <c r="AO8">
         <v>69</v>
@@ -3933,19 +3793,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM8">
+        <v>1</v>
       </c>
       <c r="EN8" t="inlineStr">
         <is>
           <t>Fraction Faceoff (Fraction intervention) with instruction in explanations</t>
-        </is>
-      </c>
-      <c r="EQ8" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU8">
@@ -3954,11 +3807,6 @@
       <c r="EW8">
         <v>2</v>
       </c>
-      <c r="EX8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY8">
         <v>4</v>
       </c>
@@ -3977,10 +3825,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE8">
+        <v>1</v>
       </c>
       <c r="FF8" t="inlineStr">
         <is>
@@ -3992,17 +3838,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH8">
+        <v>1</v>
       </c>
       <c r="FL8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4166,10 +4005,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN9">
+        <v>3</v>
       </c>
       <c r="AO9">
         <v>69</v>
@@ -4383,19 +4220,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM9">
+        <v>1</v>
       </c>
       <c r="EN9" t="inlineStr">
         <is>
           <t>Fraction Faceoff (Fraction intervention) with instruction in explanations</t>
-        </is>
-      </c>
-      <c r="EQ9" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU9">
@@ -4404,11 +4234,6 @@
       <c r="EW9">
         <v>2</v>
       </c>
-      <c r="EX9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY9">
         <v>4</v>
       </c>
@@ -4427,10 +4252,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE9">
+        <v>1</v>
       </c>
       <c r="FF9" t="inlineStr">
         <is>
@@ -4442,17 +4265,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH9">
+        <v>1</v>
       </c>
       <c r="FL9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4616,10 +4432,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN10">
+        <v>3</v>
       </c>
       <c r="AO10">
         <v>69</v>
@@ -4833,19 +4647,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM10">
+        <v>1</v>
       </c>
       <c r="EN10" t="inlineStr">
         <is>
           <t>Fraction Faceoff (Fraction intervention) with instruction in explanations</t>
-        </is>
-      </c>
-      <c r="EQ10" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU10">
@@ -4854,11 +4661,6 @@
       <c r="EW10">
         <v>2</v>
       </c>
-      <c r="EX10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY10">
         <v>4</v>
       </c>
@@ -4877,10 +4679,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE10">
+        <v>1</v>
       </c>
       <c r="FF10" t="inlineStr">
         <is>
@@ -4892,17 +4692,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH10">
+        <v>1</v>
       </c>
       <c r="FL10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5066,10 +4859,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN11">
+        <v>3</v>
       </c>
       <c r="AO11">
         <v>69</v>
@@ -5283,19 +5074,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM11">
+        <v>1</v>
       </c>
       <c r="EN11" t="inlineStr">
         <is>
           <t>Fraction Faceoff (Fraction intervention) with instruction in explanations</t>
-        </is>
-      </c>
-      <c r="EQ11" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU11">
@@ -5304,11 +5088,6 @@
       <c r="EW11">
         <v>2</v>
       </c>
-      <c r="EX11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY11">
         <v>4</v>
       </c>
@@ -5327,10 +5106,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE11">
+        <v>1</v>
       </c>
       <c r="FF11" t="inlineStr">
         <is>
@@ -5342,17 +5119,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH11">
+        <v>1</v>
       </c>
       <c r="FL11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5516,10 +5286,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN12">
+        <v>3</v>
       </c>
       <c r="AO12">
         <v>69</v>
@@ -5733,19 +5501,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM12">
+        <v>1</v>
       </c>
       <c r="EN12" t="inlineStr">
         <is>
           <t>Fraction Faceoff (Fraction intervention) with instruction in explanations</t>
-        </is>
-      </c>
-      <c r="EQ12" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU12">
@@ -5754,11 +5515,6 @@
       <c r="EW12">
         <v>2</v>
       </c>
-      <c r="EX12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY12">
         <v>4</v>
       </c>
@@ -5777,10 +5533,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE12">
+        <v>1</v>
       </c>
       <c r="FF12" t="inlineStr">
         <is>
@@ -5792,17 +5546,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH12">
+        <v>1</v>
       </c>
       <c r="FL12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5971,10 +5718,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN13">
+        <v>3</v>
       </c>
       <c r="AO13">
         <v>69</v>
@@ -6188,19 +5933,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM13">
+        <v>1</v>
       </c>
       <c r="EN13" t="inlineStr">
         <is>
           <t>Fraction Faceoff (Fraction intervention) with instruction in explanations</t>
-        </is>
-      </c>
-      <c r="EQ13" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU13">
@@ -6209,11 +5947,6 @@
       <c r="EW13">
         <v>2</v>
       </c>
-      <c r="EX13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY13">
         <v>4</v>
       </c>
@@ -6232,10 +5965,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE13">
+        <v>1</v>
       </c>
       <c r="FF13" t="inlineStr">
         <is>
@@ -6247,17 +5978,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH13">
+        <v>1</v>
       </c>
       <c r="FL13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6416,10 +6140,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN14">
+        <v>3</v>
       </c>
       <c r="AO14">
         <v>69</v>
@@ -6573,19 +6295,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM14">
+        <v>0</v>
       </c>
       <c r="EN14" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ14" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU14">
@@ -6594,11 +6309,6 @@
       <c r="EW14">
         <v>2</v>
       </c>
-      <c r="EX14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY14">
         <v>4</v>
       </c>
@@ -6617,10 +6327,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE14">
+        <v>1</v>
       </c>
       <c r="FF14" t="inlineStr">
         <is>
@@ -6632,17 +6340,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH14">
+        <v>1</v>
       </c>
       <c r="FL14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6801,10 +6502,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN15">
+        <v>3</v>
       </c>
       <c r="AO15">
         <v>69</v>
@@ -6958,19 +6657,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM15">
+        <v>0</v>
       </c>
       <c r="EN15" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ15" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU15">
@@ -6979,11 +6671,6 @@
       <c r="EW15">
         <v>2</v>
       </c>
-      <c r="EX15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY15">
         <v>4</v>
       </c>
@@ -7002,10 +6689,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE15">
+        <v>1</v>
       </c>
       <c r="FF15" t="inlineStr">
         <is>
@@ -7017,17 +6702,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH15">
+        <v>1</v>
       </c>
       <c r="FL15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7186,10 +6864,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN16">
+        <v>3</v>
       </c>
       <c r="AO16">
         <v>69</v>
@@ -7343,19 +7019,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM16">
+        <v>0</v>
       </c>
       <c r="EN16" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ16" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU16">
@@ -7364,11 +7033,6 @@
       <c r="EW16">
         <v>2</v>
       </c>
-      <c r="EX16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY16">
         <v>4</v>
       </c>
@@ -7387,10 +7051,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE16">
+        <v>1</v>
       </c>
       <c r="FF16" t="inlineStr">
         <is>
@@ -7402,17 +7064,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH16">
+        <v>1</v>
       </c>
       <c r="FL16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7571,10 +7226,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN17">
+        <v>3</v>
       </c>
       <c r="AO17">
         <v>69</v>
@@ -7728,19 +7381,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM17">
+        <v>0</v>
       </c>
       <c r="EN17" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ17" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU17">
@@ -7749,11 +7395,6 @@
       <c r="EW17">
         <v>2</v>
       </c>
-      <c r="EX17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY17">
         <v>4</v>
       </c>
@@ -7772,10 +7413,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE17">
+        <v>1</v>
       </c>
       <c r="FF17" t="inlineStr">
         <is>
@@ -7787,17 +7426,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH17">
+        <v>1</v>
       </c>
       <c r="FL17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7956,10 +7588,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN18">
+        <v>3</v>
       </c>
       <c r="AO18">
         <v>69</v>
@@ -8113,19 +7743,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM18">
+        <v>0</v>
       </c>
       <c r="EN18" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ18" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU18">
@@ -8134,11 +7757,6 @@
       <c r="EW18">
         <v>2</v>
       </c>
-      <c r="EX18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY18">
         <v>4</v>
       </c>
@@ -8157,10 +7775,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE18">
+        <v>1</v>
       </c>
       <c r="FF18" t="inlineStr">
         <is>
@@ -8172,17 +7788,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH18">
+        <v>1</v>
       </c>
       <c r="FL18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8351,10 +7960,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN19">
+        <v>3</v>
       </c>
       <c r="AO19">
         <v>69</v>
@@ -8513,19 +8120,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM19">
+        <v>0</v>
       </c>
       <c r="EN19" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ19" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU19">
@@ -8534,11 +8134,6 @@
       <c r="EW19">
         <v>2</v>
       </c>
-      <c r="EX19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY19">
         <v>4</v>
       </c>
@@ -8557,10 +8152,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE19">
+        <v>1</v>
       </c>
       <c r="FF19" t="inlineStr">
         <is>
@@ -8572,17 +8165,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH19">
+        <v>1</v>
       </c>
       <c r="FL19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8741,10 +8327,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN20">
+        <v>3</v>
       </c>
       <c r="AO20">
         <v>129</v>
@@ -8889,19 +8473,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM20">
+        <v>0</v>
       </c>
       <c r="EN20" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ20" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU20">
@@ -8910,11 +8487,6 @@
       <c r="EW20">
         <v>3</v>
       </c>
-      <c r="EX20" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY20">
         <v>4</v>
       </c>
@@ -8933,10 +8505,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE20">
+        <v>1</v>
       </c>
       <c r="FF20" t="inlineStr">
         <is>
@@ -8948,17 +8518,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH20">
+        <v>1</v>
       </c>
       <c r="FL20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9117,10 +8680,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN21">
+        <v>3</v>
       </c>
       <c r="AO21">
         <v>129</v>
@@ -9265,19 +8826,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM21">
+        <v>0</v>
       </c>
       <c r="EN21" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ21" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU21">
@@ -9286,11 +8840,6 @@
       <c r="EW21">
         <v>3</v>
       </c>
-      <c r="EX21" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY21">
         <v>4</v>
       </c>
@@ -9309,10 +8858,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE21">
+        <v>1</v>
       </c>
       <c r="FF21" t="inlineStr">
         <is>
@@ -9324,17 +8871,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH21">
+        <v>1</v>
       </c>
       <c r="FL21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9493,10 +9033,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN22">
+        <v>3</v>
       </c>
       <c r="AO22">
         <v>129</v>
@@ -9641,19 +9179,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM22">
+        <v>0</v>
       </c>
       <c r="EN22" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ22" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU22">
@@ -9662,11 +9193,6 @@
       <c r="EW22">
         <v>3</v>
       </c>
-      <c r="EX22" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY22">
         <v>4</v>
       </c>
@@ -9685,10 +9211,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE22">
+        <v>1</v>
       </c>
       <c r="FF22" t="inlineStr">
         <is>
@@ -9700,17 +9224,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH22">
+        <v>1</v>
       </c>
       <c r="FL22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9869,10 +9386,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN23">
+        <v>3</v>
       </c>
       <c r="AO23">
         <v>129</v>
@@ -10022,19 +9537,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM23">
+        <v>0</v>
       </c>
       <c r="EN23" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ23" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU23">
@@ -10043,11 +9551,6 @@
       <c r="EW23">
         <v>3</v>
       </c>
-      <c r="EX23" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY23">
         <v>4</v>
       </c>
@@ -10066,10 +9569,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE23">
+        <v>1</v>
       </c>
       <c r="FF23" t="inlineStr">
         <is>
@@ -10081,17 +9582,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH23">
+        <v>1</v>
       </c>
       <c r="FL23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10265,10 +9759,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN24">
+        <v>3</v>
       </c>
       <c r="AO24">
         <v>129</v>
@@ -10413,19 +9905,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM24">
+        <v>0</v>
       </c>
       <c r="EN24" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ24" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU24">
@@ -10434,11 +9919,6 @@
       <c r="EW24">
         <v>3</v>
       </c>
-      <c r="EX24" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY24">
         <v>4</v>
       </c>
@@ -10457,10 +9937,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE24">
+        <v>1</v>
       </c>
       <c r="FF24" t="inlineStr">
         <is>
@@ -10472,17 +9950,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH24">
+        <v>1</v>
       </c>
       <c r="FL24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10641,10 +10112,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN25">
+        <v>3</v>
       </c>
       <c r="AO25">
         <v>72</v>
@@ -10792,19 +10261,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM25">
+        <v>0</v>
       </c>
       <c r="EN25" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ25" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU25">
@@ -10813,11 +10275,6 @@
       <c r="EW25">
         <v>2</v>
       </c>
-      <c r="EX25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY25">
         <v>4</v>
       </c>
@@ -10836,10 +10293,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE25">
+        <v>1</v>
       </c>
       <c r="FF25" t="inlineStr">
         <is>
@@ -10851,17 +10306,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH25">
+        <v>1</v>
       </c>
       <c r="FL25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11020,10 +10468,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN26">
+        <v>3</v>
       </c>
       <c r="AO26">
         <v>72</v>
@@ -11171,19 +10617,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM26">
+        <v>0</v>
       </c>
       <c r="EN26" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ26" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU26">
@@ -11192,11 +10631,6 @@
       <c r="EW26">
         <v>2</v>
       </c>
-      <c r="EX26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY26">
         <v>4</v>
       </c>
@@ -11215,10 +10649,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE26">
+        <v>1</v>
       </c>
       <c r="FF26" t="inlineStr">
         <is>
@@ -11230,17 +10662,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH26">
+        <v>1</v>
       </c>
       <c r="FL26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11399,10 +10824,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN27">
+        <v>3</v>
       </c>
       <c r="AO27">
         <v>72</v>
@@ -11550,19 +10973,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM27">
+        <v>0</v>
       </c>
       <c r="EN27" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ27" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU27">
@@ -11571,11 +10987,6 @@
       <c r="EW27">
         <v>2</v>
       </c>
-      <c r="EX27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY27">
         <v>4</v>
       </c>
@@ -11594,10 +11005,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE27">
+        <v>1</v>
       </c>
       <c r="FF27" t="inlineStr">
         <is>
@@ -11609,17 +11018,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH27">
+        <v>1</v>
       </c>
       <c r="FL27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11778,10 +11180,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN28">
+        <v>3</v>
       </c>
       <c r="AO28">
         <v>72</v>
@@ -11929,19 +11329,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM28">
+        <v>0</v>
       </c>
       <c r="EN28" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ28" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU28">
@@ -11950,11 +11343,6 @@
       <c r="EW28">
         <v>2</v>
       </c>
-      <c r="EX28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY28">
         <v>4</v>
       </c>
@@ -11973,10 +11361,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE28">
+        <v>1</v>
       </c>
       <c r="FF28" t="inlineStr">
         <is>
@@ -11988,17 +11374,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH28">
+        <v>1</v>
       </c>
       <c r="FL28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -12167,10 +11546,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN29">
+        <v>3</v>
       </c>
       <c r="AO29">
         <v>72</v>
@@ -12323,19 +11700,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM29">
+        <v>0</v>
       </c>
       <c r="EN29" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ29" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU29">
@@ -12344,11 +11714,6 @@
       <c r="EW29">
         <v>2</v>
       </c>
-      <c r="EX29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY29">
         <v>4</v>
       </c>
@@ -12367,10 +11732,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE29">
+        <v>1</v>
       </c>
       <c r="FF29" t="inlineStr">
         <is>
@@ -12382,17 +11745,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH29">
+        <v>1</v>
       </c>
       <c r="FL29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -12548,10 +11904,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN30">
+        <v>3</v>
       </c>
       <c r="AO30">
         <v>71</v>
@@ -12699,19 +12053,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM30">
+        <v>0</v>
       </c>
       <c r="EN30" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ30" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU30">
@@ -12720,11 +12067,6 @@
       <c r="EW30">
         <v>2</v>
       </c>
-      <c r="EX30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY30">
         <v>4</v>
       </c>
@@ -12743,10 +12085,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE30">
+        <v>1</v>
       </c>
       <c r="FF30" t="inlineStr">
         <is>
@@ -12758,17 +12098,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH30">
+        <v>1</v>
       </c>
       <c r="FL30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -12924,10 +12257,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN31">
+        <v>3</v>
       </c>
       <c r="AO31">
         <v>71</v>
@@ -13075,19 +12406,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM31">
+        <v>0</v>
       </c>
       <c r="EN31" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ31" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU31">
@@ -13096,11 +12420,6 @@
       <c r="EW31">
         <v>2</v>
       </c>
-      <c r="EX31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY31">
         <v>4</v>
       </c>
@@ -13119,10 +12438,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE31">
+        <v>1</v>
       </c>
       <c r="FF31" t="inlineStr">
         <is>
@@ -13134,17 +12451,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH31">
+        <v>1</v>
       </c>
       <c r="FL31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13300,10 +12610,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN32">
+        <v>3</v>
       </c>
       <c r="AO32">
         <v>71</v>
@@ -13451,19 +12759,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM32">
+        <v>0</v>
       </c>
       <c r="EN32" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ32" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU32">
@@ -13472,11 +12773,6 @@
       <c r="EW32">
         <v>2</v>
       </c>
-      <c r="EX32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY32">
         <v>4</v>
       </c>
@@ -13495,10 +12791,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE32">
+        <v>1</v>
       </c>
       <c r="FF32" t="inlineStr">
         <is>
@@ -13510,17 +12804,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH32">
+        <v>1</v>
       </c>
       <c r="FL32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13676,10 +12963,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN33">
+        <v>3</v>
       </c>
       <c r="AO33">
         <v>71</v>
@@ -13835,19 +13120,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM33">
+        <v>0</v>
       </c>
       <c r="EN33" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ33" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU33">
@@ -13856,11 +13134,6 @@
       <c r="EW33">
         <v>2</v>
       </c>
-      <c r="EX33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY33">
         <v>4</v>
       </c>
@@ -13879,10 +13152,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE33">
+        <v>1</v>
       </c>
       <c r="FF33" t="inlineStr">
         <is>
@@ -13894,17 +13165,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH33">
+        <v>1</v>
       </c>
       <c r="FL33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -14070,10 +13334,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN34">
+        <v>3</v>
       </c>
       <c r="AO34">
         <v>71</v>
@@ -14221,19 +13483,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM34">
+        <v>0</v>
       </c>
       <c r="EN34" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ34" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU34">
@@ -14242,11 +13497,6 @@
       <c r="EW34">
         <v>2</v>
       </c>
-      <c r="EX34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY34">
         <v>4</v>
       </c>
@@ -14265,10 +13515,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE34">
+        <v>1</v>
       </c>
       <c r="FF34" t="inlineStr">
         <is>
@@ -14280,17 +13528,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH34">
+        <v>1</v>
       </c>
       <c r="FL34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -14449,10 +13690,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN35">
+        <v>3</v>
       </c>
       <c r="AO35">
         <v>15</v>
@@ -14561,29 +13800,17 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM35">
+        <v>0</v>
       </c>
       <c r="EN35" t="inlineStr">
         <is>
           <t>Small-group supplemental reading instruction</t>
-        </is>
-      </c>
-      <c r="EQ35" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU35">
         <v>5</v>
       </c>
-      <c r="EX35" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
       <c r="EY35">
         <v>6</v>
       </c>
@@ -14602,10 +13829,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE35">
+        <v>1</v>
       </c>
       <c r="FF35" t="inlineStr">
         <is>
@@ -14617,19 +13842,12 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH35">
+        <v>1</v>
       </c>
       <c r="FL35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="FQ35" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR35" t="b">
@@ -14801,10 +14019,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN36">
+        <v>3</v>
       </c>
       <c r="AO36">
         <v>15</v>
@@ -14918,29 +14134,17 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM36">
+        <v>0</v>
       </c>
       <c r="EN36" t="inlineStr">
         <is>
           <t>Small-group supplemental reading instruction</t>
-        </is>
-      </c>
-      <c r="EQ36" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU36">
         <v>5</v>
       </c>
-      <c r="EX36" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
       <c r="EY36">
         <v>6</v>
       </c>
@@ -14959,10 +14163,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE36">
+        <v>1</v>
       </c>
       <c r="FF36" t="inlineStr">
         <is>
@@ -14974,19 +14176,12 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH36">
+        <v>1</v>
       </c>
       <c r="FL36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="FQ36" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR36" t="b">
@@ -15143,10 +14338,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN37">
+        <v>3</v>
       </c>
       <c r="AO37">
         <v>28</v>
@@ -15278,19 +14471,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM37">
+        <v>0</v>
       </c>
       <c r="EN37" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ37" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU37">
@@ -15299,11 +14485,6 @@
       <c r="EW37">
         <v>3.5</v>
       </c>
-      <c r="EX37" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY37">
         <v>6</v>
       </c>
@@ -15322,10 +14503,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE37">
+        <v>1</v>
       </c>
       <c r="FF37" t="inlineStr">
         <is>
@@ -15337,19 +14516,12 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH37">
+        <v>1</v>
       </c>
       <c r="FL37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="FQ37" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="FR37" t="b">
@@ -15506,10 +14678,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN38">
+        <v>3</v>
       </c>
       <c r="AO38">
         <v>28</v>
@@ -15646,19 +14816,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM38">
+        <v>0</v>
       </c>
       <c r="EN38" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ38" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU38">
@@ -15667,11 +14830,6 @@
       <c r="EW38">
         <v>3.5</v>
       </c>
-      <c r="EX38" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY38">
         <v>6</v>
       </c>
@@ -15690,10 +14848,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE38">
+        <v>1</v>
       </c>
       <c r="FF38" t="inlineStr">
         <is>
@@ -15705,19 +14861,12 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH38">
+        <v>1</v>
       </c>
       <c r="FL38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="FQ38" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="FR38" t="b">
@@ -15874,10 +15023,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN39">
+        <v>3</v>
       </c>
       <c r="AO39">
         <v>25</v>
@@ -16004,19 +15151,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM39">
+        <v>0</v>
       </c>
       <c r="EN39" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ39" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU39">
@@ -16025,11 +15165,6 @@
       <c r="EW39">
         <v>4</v>
       </c>
-      <c r="EX39" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY39">
         <v>6</v>
       </c>
@@ -16048,34 +15183,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE39" t="inlineStr">
+      <c r="FE39">
+        <v>1</v>
+      </c>
+      <c r="FF39" t="inlineStr">
+        <is>
+          <t>Researcher-Instructors (graduate students, postdoctoral researchers, and former math teachers)</t>
+        </is>
+      </c>
+      <c r="FG39" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH39">
+        <v>1</v>
+      </c>
+      <c r="FL39" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF39" t="inlineStr">
-        <is>
-          <t>Researcher-Instructors (graduate students, postdoctoral researchers, and former math teachers)</t>
-        </is>
-      </c>
-      <c r="FG39" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ39" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="FR39" t="b">
@@ -16232,10 +15358,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN40">
+        <v>3</v>
       </c>
       <c r="AO40">
         <v>25</v>
@@ -16362,19 +15486,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM40">
+        <v>0</v>
       </c>
       <c r="EN40" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ40" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU40">
@@ -16383,11 +15500,6 @@
       <c r="EW40">
         <v>4</v>
       </c>
-      <c r="EX40" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY40">
         <v>6</v>
       </c>
@@ -16406,34 +15518,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE40" t="inlineStr">
+      <c r="FE40">
+        <v>1</v>
+      </c>
+      <c r="FF40" t="inlineStr">
+        <is>
+          <t>Researcher-Instructors (graduate students, postdoctoral researchers, and former math teachers)</t>
+        </is>
+      </c>
+      <c r="FG40" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH40">
+        <v>1</v>
+      </c>
+      <c r="FL40" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF40" t="inlineStr">
-        <is>
-          <t>Researcher-Instructors (graduate students, postdoctoral researchers, and former math teachers)</t>
-        </is>
-      </c>
-      <c r="FG40" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ40" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="FR40" t="b">
@@ -16590,10 +15693,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN41">
+        <v>3</v>
       </c>
       <c r="AO41">
         <v>25</v>
@@ -16725,19 +15826,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM41">
+        <v>0</v>
       </c>
       <c r="EN41" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ41" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU41">
@@ -16746,11 +15840,6 @@
       <c r="EW41">
         <v>4</v>
       </c>
-      <c r="EX41" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY41">
         <v>6</v>
       </c>
@@ -16769,34 +15858,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE41" t="inlineStr">
+      <c r="FE41">
+        <v>1</v>
+      </c>
+      <c r="FF41" t="inlineStr">
+        <is>
+          <t>Researcher-Instructors (graduate students, postdoctoral researchers, and former math teachers)</t>
+        </is>
+      </c>
+      <c r="FG41" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH41">
+        <v>1</v>
+      </c>
+      <c r="FL41" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF41" t="inlineStr">
-        <is>
-          <t>Researcher-Instructors (graduate students, postdoctoral researchers, and former math teachers)</t>
-        </is>
-      </c>
-      <c r="FG41" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ41" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="FR41" t="b">
@@ -16948,10 +16028,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN42">
+        <v>3</v>
       </c>
       <c r="AO42">
         <v>86</v>
@@ -17069,19 +16147,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM42">
+        <v>0</v>
       </c>
       <c r="EN42" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ42" t="inlineStr">
-        <is>
-          <t>1677888000</t>
         </is>
       </c>
       <c r="EU42">
@@ -17090,11 +16161,6 @@
       <c r="EW42">
         <v>5</v>
       </c>
-      <c r="EX42" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY42">
         <v>5</v>
       </c>
@@ -17113,34 +16179,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE42" t="inlineStr">
+      <c r="FE42">
+        <v>1</v>
+      </c>
+      <c r="FF42" t="inlineStr">
+        <is>
+          <t>Tutors (recruited from community)</t>
+        </is>
+      </c>
+      <c r="FG42" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH42">
+        <v>1</v>
+      </c>
+      <c r="FL42" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF42" t="inlineStr">
-        <is>
-          <t>Tutors (recruited from community)</t>
-        </is>
-      </c>
-      <c r="FG42" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ42" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR42" t="b">
@@ -17292,10 +16349,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN43">
+        <v>3</v>
       </c>
       <c r="AO43">
         <v>86</v>
@@ -17413,19 +16468,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM43">
+        <v>0</v>
       </c>
       <c r="EN43" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ43" t="inlineStr">
-        <is>
-          <t>1677888000</t>
         </is>
       </c>
       <c r="EU43">
@@ -17434,11 +16482,6 @@
       <c r="EW43">
         <v>5</v>
       </c>
-      <c r="EX43" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY43">
         <v>5</v>
       </c>
@@ -17457,34 +16500,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE43" t="inlineStr">
+      <c r="FE43">
+        <v>1</v>
+      </c>
+      <c r="FF43" t="inlineStr">
+        <is>
+          <t>Tutors (recruited from community)</t>
+        </is>
+      </c>
+      <c r="FG43" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH43">
+        <v>1</v>
+      </c>
+      <c r="FL43" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF43" t="inlineStr">
-        <is>
-          <t>Tutors (recruited from community)</t>
-        </is>
-      </c>
-      <c r="FG43" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ43" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR43" t="b">
@@ -17636,10 +16670,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN44">
+        <v>3</v>
       </c>
       <c r="AO44">
         <v>86</v>
@@ -17757,19 +16789,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM44">
+        <v>0</v>
       </c>
       <c r="EN44" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ44" t="inlineStr">
-        <is>
-          <t>1677888000</t>
         </is>
       </c>
       <c r="EU44">
@@ -17778,11 +16803,6 @@
       <c r="EW44">
         <v>5</v>
       </c>
-      <c r="EX44" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY44">
         <v>5</v>
       </c>
@@ -17801,34 +16821,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE44" t="inlineStr">
+      <c r="FE44">
+        <v>1</v>
+      </c>
+      <c r="FF44" t="inlineStr">
+        <is>
+          <t>Tutors (recruited from community)</t>
+        </is>
+      </c>
+      <c r="FG44" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH44">
+        <v>1</v>
+      </c>
+      <c r="FL44" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF44" t="inlineStr">
-        <is>
-          <t>Tutors (recruited from community)</t>
-        </is>
-      </c>
-      <c r="FG44" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ44" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR44" t="b">
@@ -17980,10 +16991,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN45">
+        <v>3</v>
       </c>
       <c r="AO45">
         <v>86</v>
@@ -18101,19 +17110,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM45">
+        <v>0</v>
       </c>
       <c r="EN45" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ45" t="inlineStr">
-        <is>
-          <t>1677888000</t>
         </is>
       </c>
       <c r="EU45">
@@ -18122,11 +17124,6 @@
       <c r="EW45">
         <v>5</v>
       </c>
-      <c r="EX45" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY45">
         <v>5</v>
       </c>
@@ -18145,34 +17142,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE45" t="inlineStr">
+      <c r="FE45">
+        <v>1</v>
+      </c>
+      <c r="FF45" t="inlineStr">
+        <is>
+          <t>Tutors (recruited from community)</t>
+        </is>
+      </c>
+      <c r="FG45" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH45">
+        <v>1</v>
+      </c>
+      <c r="FL45" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF45" t="inlineStr">
-        <is>
-          <t>Tutors (recruited from community)</t>
-        </is>
-      </c>
-      <c r="FG45" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ45" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR45" t="b">
@@ -18339,10 +17327,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN46">
+        <v>3</v>
       </c>
       <c r="AO46">
         <v>87</v>
@@ -18465,19 +17451,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM46">
+        <v>0</v>
       </c>
       <c r="EN46" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ46" t="inlineStr">
-        <is>
-          <t>44989</t>
         </is>
       </c>
       <c r="EU46">
@@ -18486,11 +17465,6 @@
       <c r="EW46">
         <v>5</v>
       </c>
-      <c r="EX46" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY46">
         <v>5</v>
       </c>
@@ -18509,34 +17483,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE46" t="inlineStr">
+      <c r="FE46">
+        <v>1</v>
+      </c>
+      <c r="FF46" t="inlineStr">
+        <is>
+          <t>Tutors (recruited from community)</t>
+        </is>
+      </c>
+      <c r="FG46" t="inlineStr">
+        <is>
+          <t>research staff</t>
+        </is>
+      </c>
+      <c r="FH46">
+        <v>1</v>
+      </c>
+      <c r="FL46" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF46" t="inlineStr">
-        <is>
-          <t>Tutors (recruited from community)</t>
-        </is>
-      </c>
-      <c r="FG46" t="inlineStr">
-        <is>
-          <t>research staff</t>
-        </is>
-      </c>
-      <c r="FH46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FL46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ46" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR46" t="b">
@@ -18693,10 +17658,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN47">
+        <v>3</v>
       </c>
       <c r="AO47">
         <v>29</v>
@@ -18850,19 +17813,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM47">
+        <v>0</v>
       </c>
       <c r="EN47" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ47" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU47">
@@ -18871,11 +17827,6 @@
       <c r="EW47">
         <v>2</v>
       </c>
-      <c r="EX47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY47">
         <v>3</v>
       </c>
@@ -18894,10 +17845,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE47">
+        <v>1</v>
       </c>
       <c r="FF47" t="inlineStr">
         <is>
@@ -18909,17 +17858,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH47">
+        <v>1</v>
       </c>
       <c r="FL47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19078,10 +18020,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN48">
+        <v>3</v>
       </c>
       <c r="AO48">
         <v>29</v>
@@ -19235,19 +18175,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM48">
+        <v>0</v>
       </c>
       <c r="EN48" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ48" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU48">
@@ -19256,11 +18189,6 @@
       <c r="EW48">
         <v>2</v>
       </c>
-      <c r="EX48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY48">
         <v>3</v>
       </c>
@@ -19279,10 +18207,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE48">
+        <v>1</v>
       </c>
       <c r="FF48" t="inlineStr">
         <is>
@@ -19294,17 +18220,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH48">
+        <v>1</v>
       </c>
       <c r="FL48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19463,10 +18382,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN49">
+        <v>3</v>
       </c>
       <c r="AO49">
         <v>29</v>
@@ -19620,19 +18537,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM49">
+        <v>0</v>
       </c>
       <c r="EN49" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ49" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU49">
@@ -19641,11 +18551,6 @@
       <c r="EW49">
         <v>2</v>
       </c>
-      <c r="EX49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY49">
         <v>3</v>
       </c>
@@ -19664,10 +18569,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE49">
+        <v>1</v>
       </c>
       <c r="FF49" t="inlineStr">
         <is>
@@ -19679,17 +18582,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH49">
+        <v>1</v>
       </c>
       <c r="FL49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ49" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19848,10 +18744,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN50">
+        <v>3</v>
       </c>
       <c r="AO50">
         <v>29</v>
@@ -20005,19 +18899,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM50">
+        <v>0</v>
       </c>
       <c r="EN50" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ50" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU50">
@@ -20026,11 +18913,6 @@
       <c r="EW50">
         <v>2</v>
       </c>
-      <c r="EX50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY50">
         <v>3</v>
       </c>
@@ -20049,10 +18931,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE50">
+        <v>1</v>
       </c>
       <c r="FF50" t="inlineStr">
         <is>
@@ -20064,17 +18944,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH50">
+        <v>1</v>
       </c>
       <c r="FL50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -20241,10 +19114,8 @@
           <t>Whole Numbers Computation</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AN51">
+        <v>2</v>
       </c>
       <c r="AO51">
         <v>29</v>
@@ -20398,19 +19269,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM51">
+        <v>0</v>
       </c>
       <c r="EN51" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ51" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU51">
@@ -20419,11 +19283,6 @@
       <c r="EW51">
         <v>2</v>
       </c>
-      <c r="EX51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY51">
         <v>3</v>
       </c>
@@ -20442,10 +19301,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE51">
+        <v>1</v>
       </c>
       <c r="FF51" t="inlineStr">
         <is>
@@ -20457,17 +19314,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH51">
+        <v>1</v>
       </c>
       <c r="FL51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ51" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -20636,10 +19486,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN52">
+        <v>3</v>
       </c>
       <c r="AO52">
         <v>29</v>
@@ -20798,19 +19646,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM52">
+        <v>0</v>
       </c>
       <c r="EN52" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ52" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU52">
@@ -20819,11 +19660,6 @@
       <c r="EW52">
         <v>2</v>
       </c>
-      <c r="EX52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY52">
         <v>3</v>
       </c>
@@ -20842,10 +19678,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE52">
+        <v>1</v>
       </c>
       <c r="FF52" t="inlineStr">
         <is>
@@ -20857,17 +19691,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH52">
+        <v>1</v>
       </c>
       <c r="FL52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -21026,10 +19853,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN53">
+        <v>3</v>
       </c>
       <c r="AO53">
         <v>26</v>
@@ -21183,19 +20008,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM53">
+        <v>0</v>
       </c>
       <c r="EN53" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ53" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU53">
@@ -21204,11 +20022,6 @@
       <c r="EW53">
         <v>2</v>
       </c>
-      <c r="EX53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY53">
         <v>3</v>
       </c>
@@ -21227,10 +20040,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE53">
+        <v>1</v>
       </c>
       <c r="FF53" t="inlineStr">
         <is>
@@ -21242,17 +20053,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH53">
+        <v>1</v>
       </c>
       <c r="FL53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -21411,10 +20215,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN54">
+        <v>3</v>
       </c>
       <c r="AO54">
         <v>26</v>
@@ -21568,19 +20370,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM54">
+        <v>0</v>
       </c>
       <c r="EN54" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ54" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU54">
@@ -21589,11 +20384,6 @@
       <c r="EW54">
         <v>2</v>
       </c>
-      <c r="EX54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY54">
         <v>3</v>
       </c>
@@ -21612,10 +20402,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE54">
+        <v>1</v>
       </c>
       <c r="FF54" t="inlineStr">
         <is>
@@ -21627,17 +20415,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH54">
+        <v>1</v>
       </c>
       <c r="FL54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -21796,10 +20577,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN55">
+        <v>3</v>
       </c>
       <c r="AO55">
         <v>26</v>
@@ -21953,19 +20732,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM55">
+        <v>0</v>
       </c>
       <c r="EN55" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ55" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU55">
@@ -21974,11 +20746,6 @@
       <c r="EW55">
         <v>2</v>
       </c>
-      <c r="EX55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY55">
         <v>3</v>
       </c>
@@ -21997,10 +20764,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE55">
+        <v>1</v>
       </c>
       <c r="FF55" t="inlineStr">
         <is>
@@ -22012,17 +20777,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH55">
+        <v>1</v>
       </c>
       <c r="FL55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -22181,10 +20939,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN56">
+        <v>3</v>
       </c>
       <c r="AO56">
         <v>26</v>
@@ -22338,19 +21094,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM56">
+        <v>0</v>
       </c>
       <c r="EN56" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ56" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU56">
@@ -22359,11 +21108,6 @@
       <c r="EW56">
         <v>2</v>
       </c>
-      <c r="EX56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY56">
         <v>3</v>
       </c>
@@ -22382,10 +21126,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE56">
+        <v>1</v>
       </c>
       <c r="FF56" t="inlineStr">
         <is>
@@ -22397,17 +21139,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH56">
+        <v>1</v>
       </c>
       <c r="FL56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ56" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -22574,10 +21309,8 @@
           <t>Whole Numbers Computation</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AN57">
+        <v>2</v>
       </c>
       <c r="AO57">
         <v>26</v>
@@ -22731,19 +21464,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM57">
+        <v>0</v>
       </c>
       <c r="EN57" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ57" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU57">
@@ -22752,11 +21478,6 @@
       <c r="EW57">
         <v>2</v>
       </c>
-      <c r="EX57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY57">
         <v>3</v>
       </c>
@@ -22775,10 +21496,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE57">
+        <v>1</v>
       </c>
       <c r="FF57" t="inlineStr">
         <is>
@@ -22790,17 +21509,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH57">
+        <v>1</v>
       </c>
       <c r="FL57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ57" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -22974,10 +21686,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN58">
+        <v>3</v>
       </c>
       <c r="AO58">
         <v>26</v>
@@ -23139,19 +21849,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM58">
+        <v>0</v>
       </c>
       <c r="EN58" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ58" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU58">
@@ -23160,11 +21863,6 @@
       <c r="EW58">
         <v>2</v>
       </c>
-      <c r="EX58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY58">
         <v>3</v>
       </c>
@@ -23183,10 +21881,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE58">
+        <v>1</v>
       </c>
       <c r="FF58" t="inlineStr">
         <is>
@@ -23198,17 +21894,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH58">
+        <v>1</v>
       </c>
       <c r="FL58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -23372,10 +22061,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN59">
+        <v>3</v>
       </c>
       <c r="AO59">
         <v>46</v>
@@ -23600,19 +22287,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM59">
+        <v>1</v>
       </c>
       <c r="EN59" t="inlineStr">
         <is>
           <t>Super Solvers (fraction magnitude intervention with word problems) with error analysis</t>
-        </is>
-      </c>
-      <c r="EQ59" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU59">
@@ -23621,11 +22301,6 @@
       <c r="EW59">
         <v>2</v>
       </c>
-      <c r="EX59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY59">
         <v>4.5</v>
       </c>
@@ -23644,10 +22319,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE59">
+        <v>1</v>
       </c>
       <c r="FF59" t="inlineStr">
         <is>
@@ -23659,17 +22332,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH59">
+        <v>1</v>
       </c>
       <c r="FL59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ59" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -23833,10 +22499,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN60">
+        <v>3</v>
       </c>
       <c r="AO60">
         <v>46</v>
@@ -24061,19 +22725,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM60">
+        <v>1</v>
       </c>
       <c r="EN60" t="inlineStr">
         <is>
           <t>Super Solvers (fraction magnitude intervention with word problems) with error analysis</t>
-        </is>
-      </c>
-      <c r="EQ60" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU60">
@@ -24082,11 +22739,6 @@
       <c r="EW60">
         <v>2</v>
       </c>
-      <c r="EX60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY60">
         <v>4.5</v>
       </c>
@@ -24105,10 +22757,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE60">
+        <v>1</v>
       </c>
       <c r="FF60" t="inlineStr">
         <is>
@@ -24120,17 +22770,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH60">
+        <v>1</v>
       </c>
       <c r="FL60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ60" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -24294,10 +22937,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN61">
+        <v>3</v>
       </c>
       <c r="AO61">
         <v>46</v>
@@ -24522,19 +23163,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM61">
+        <v>1</v>
       </c>
       <c r="EN61" t="inlineStr">
         <is>
           <t>Super Solvers (fraction magnitude intervention with word problems) with error analysis</t>
-        </is>
-      </c>
-      <c r="EQ61" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU61">
@@ -24543,11 +23177,6 @@
       <c r="EW61">
         <v>2</v>
       </c>
-      <c r="EX61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY61">
         <v>4.5</v>
       </c>
@@ -24566,10 +23195,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE61">
+        <v>1</v>
       </c>
       <c r="FF61" t="inlineStr">
         <is>
@@ -24581,17 +23208,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH61">
+        <v>1</v>
       </c>
       <c r="FL61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -24765,10 +23385,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN62">
+        <v>3</v>
       </c>
       <c r="AO62">
         <v>46</v>
@@ -24995,19 +23613,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM62">
+        <v>1</v>
       </c>
       <c r="EN62" t="inlineStr">
         <is>
           <t>Super Solvers (fraction magnitude intervention with word problems) with error analysis</t>
-        </is>
-      </c>
-      <c r="EQ62" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU62">
@@ -25016,11 +23627,6 @@
       <c r="EW62">
         <v>2</v>
       </c>
-      <c r="EX62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY62">
         <v>4.5</v>
       </c>
@@ -25039,10 +23645,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE62">
+        <v>1</v>
       </c>
       <c r="FF62" t="inlineStr">
         <is>
@@ -25054,17 +23658,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH62">
+        <v>1</v>
       </c>
       <c r="FL62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -25223,10 +23820,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN63">
+        <v>3</v>
       </c>
       <c r="AO63">
         <v>45</v>
@@ -25388,19 +23983,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM63">
+        <v>0</v>
       </c>
       <c r="EN63" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ63" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU63">
@@ -25409,11 +23997,6 @@
       <c r="EW63">
         <v>2</v>
       </c>
-      <c r="EX63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY63">
         <v>4.5</v>
       </c>
@@ -25432,10 +24015,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE63">
+        <v>1</v>
       </c>
       <c r="FF63" t="inlineStr">
         <is>
@@ -25447,17 +24028,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH63">
+        <v>1</v>
       </c>
       <c r="FL63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -25616,10 +24190,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN64">
+        <v>3</v>
       </c>
       <c r="AO64">
         <v>45</v>
@@ -25781,19 +24353,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM64">
+        <v>0</v>
       </c>
       <c r="EN64" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ64" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU64">
@@ -25802,11 +24367,6 @@
       <c r="EW64">
         <v>2</v>
       </c>
-      <c r="EX64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY64">
         <v>4.5</v>
       </c>
@@ -25825,10 +24385,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE64">
+        <v>1</v>
       </c>
       <c r="FF64" t="inlineStr">
         <is>
@@ -25840,17 +24398,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH64">
+        <v>1</v>
       </c>
       <c r="FL64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -26009,10 +24560,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN65">
+        <v>3</v>
       </c>
       <c r="AO65">
         <v>45</v>
@@ -26174,19 +24723,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM65">
+        <v>0</v>
       </c>
       <c r="EN65" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ65" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU65">
@@ -26195,11 +24737,6 @@
       <c r="EW65">
         <v>2</v>
       </c>
-      <c r="EX65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY65">
         <v>4.5</v>
       </c>
@@ -26218,10 +24755,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE65">
+        <v>1</v>
       </c>
       <c r="FF65" t="inlineStr">
         <is>
@@ -26233,17 +24768,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH65">
+        <v>1</v>
       </c>
       <c r="FL65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -26412,10 +24940,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN66">
+        <v>3</v>
       </c>
       <c r="AO66">
         <v>45</v>
@@ -26582,19 +25108,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM66">
+        <v>0</v>
       </c>
       <c r="EN66" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ66" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU66">
@@ -26603,11 +25122,6 @@
       <c r="EW66">
         <v>2</v>
       </c>
-      <c r="EX66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY66">
         <v>4.5</v>
       </c>
@@ -26626,10 +25140,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE66">
+        <v>1</v>
       </c>
       <c r="FF66" t="inlineStr">
         <is>
@@ -26641,17 +25153,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH66">
+        <v>1</v>
       </c>
       <c r="FL66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ66" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -26805,10 +25310,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN67">
+        <v>3</v>
       </c>
       <c r="AO67">
         <v>46</v>
@@ -26967,19 +25470,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM67">
+        <v>0</v>
       </c>
       <c r="EN67" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ67" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU67">
@@ -26988,11 +25484,6 @@
       <c r="EW67">
         <v>2</v>
       </c>
-      <c r="EX67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY67">
         <v>4.5</v>
       </c>
@@ -27011,10 +25502,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE67">
+        <v>1</v>
       </c>
       <c r="FF67" t="inlineStr">
         <is>
@@ -27026,17 +25515,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH67">
+        <v>1</v>
       </c>
       <c r="FL67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -27190,10 +25672,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN68">
+        <v>3</v>
       </c>
       <c r="AO68">
         <v>46</v>
@@ -27352,19 +25832,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM68">
+        <v>0</v>
       </c>
       <c r="EN68" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ68" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU68">
@@ -27373,11 +25846,6 @@
       <c r="EW68">
         <v>2</v>
       </c>
-      <c r="EX68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY68">
         <v>4.5</v>
       </c>
@@ -27396,10 +25864,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE68">
+        <v>1</v>
       </c>
       <c r="FF68" t="inlineStr">
         <is>
@@ -27411,17 +25877,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH68">
+        <v>1</v>
       </c>
       <c r="FL68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -27575,10 +26034,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN69">
+        <v>3</v>
       </c>
       <c r="AO69">
         <v>46</v>
@@ -27737,19 +26194,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM69">
+        <v>0</v>
       </c>
       <c r="EN69" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ69" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU69">
@@ -27758,11 +26208,6 @@
       <c r="EW69">
         <v>2</v>
       </c>
-      <c r="EX69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY69">
         <v>4.5</v>
       </c>
@@ -27781,10 +26226,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE69">
+        <v>1</v>
       </c>
       <c r="FF69" t="inlineStr">
         <is>
@@ -27796,17 +26239,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH69">
+        <v>1</v>
       </c>
       <c r="FL69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ69" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -27975,10 +26411,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN70">
+        <v>3</v>
       </c>
       <c r="AO70">
         <v>46</v>
@@ -28145,19 +26579,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM70">
+        <v>0</v>
       </c>
       <c r="EN70" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ70" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU70">
@@ -28166,11 +26593,6 @@
       <c r="EW70">
         <v>2</v>
       </c>
-      <c r="EX70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY70">
         <v>4.5</v>
       </c>
@@ -28189,10 +26611,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE70">
+        <v>1</v>
       </c>
       <c r="FF70" t="inlineStr">
         <is>
@@ -28204,17 +26624,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH70">
+        <v>1</v>
       </c>
       <c r="FL70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -28368,10 +26781,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN71">
+        <v>3</v>
       </c>
       <c r="AO71">
         <v>76</v>
@@ -28522,19 +26933,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM71">
+        <v>0</v>
       </c>
       <c r="EN71" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ71" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU71">
@@ -28543,11 +26947,6 @@
       <c r="EW71">
         <v>2</v>
       </c>
-      <c r="EX71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY71">
         <v>4</v>
       </c>
@@ -28566,10 +26965,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE71">
+        <v>1</v>
       </c>
       <c r="FF71" t="inlineStr">
         <is>
@@ -28581,17 +26978,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH71">
+        <v>1</v>
       </c>
       <c r="FL71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ71" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -28745,10 +27135,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN72">
+        <v>3</v>
       </c>
       <c r="AO72">
         <v>76</v>
@@ -28899,19 +27287,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM72">
+        <v>0</v>
       </c>
       <c r="EN72" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ72" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU72">
@@ -28920,11 +27301,6 @@
       <c r="EW72">
         <v>2</v>
       </c>
-      <c r="EX72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY72">
         <v>4</v>
       </c>
@@ -28943,10 +27319,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE72">
+        <v>1</v>
       </c>
       <c r="FF72" t="inlineStr">
         <is>
@@ -28958,17 +27332,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH72">
+        <v>1</v>
       </c>
       <c r="FL72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ72" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -29122,10 +27489,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN73">
+        <v>3</v>
       </c>
       <c r="AO73">
         <v>76</v>
@@ -29276,19 +27641,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM73">
+        <v>0</v>
       </c>
       <c r="EN73" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ73" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU73">
@@ -29297,11 +27655,6 @@
       <c r="EW73">
         <v>2</v>
       </c>
-      <c r="EX73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY73">
         <v>4</v>
       </c>
@@ -29320,10 +27673,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE73">
+        <v>1</v>
       </c>
       <c r="FF73" t="inlineStr">
         <is>
@@ -29335,17 +27686,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH73">
+        <v>1</v>
       </c>
       <c r="FL73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ73" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -29499,10 +27843,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN74">
+        <v>3</v>
       </c>
       <c r="AO74">
         <v>76</v>
@@ -29653,19 +27995,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM74">
+        <v>0</v>
       </c>
       <c r="EN74" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ74" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU74">
@@ -29674,11 +28009,6 @@
       <c r="EW74">
         <v>2</v>
       </c>
-      <c r="EX74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY74">
         <v>4</v>
       </c>
@@ -29697,10 +28027,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE74">
+        <v>1</v>
       </c>
       <c r="FF74" t="inlineStr">
         <is>
@@ -29712,17 +28040,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH74">
+        <v>1</v>
       </c>
       <c r="FL74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ74" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -29876,10 +28197,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN75">
+        <v>3</v>
       </c>
       <c r="AO75">
         <v>76</v>
@@ -30030,19 +28349,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM75">
+        <v>0</v>
       </c>
       <c r="EN75" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ75" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU75">
@@ -30051,11 +28363,6 @@
       <c r="EW75">
         <v>2</v>
       </c>
-      <c r="EX75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY75">
         <v>4</v>
       </c>
@@ -30074,10 +28381,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE75">
+        <v>1</v>
       </c>
       <c r="FF75" t="inlineStr">
         <is>
@@ -30089,17 +28394,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH75">
+        <v>1</v>
       </c>
       <c r="FL75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -30253,10 +28551,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN76">
+        <v>3</v>
       </c>
       <c r="AO76">
         <v>76</v>
@@ -30407,19 +28703,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM76">
+        <v>0</v>
       </c>
       <c r="EN76" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ76" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU76">
@@ -30428,11 +28717,6 @@
       <c r="EW76">
         <v>2</v>
       </c>
-      <c r="EX76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY76">
         <v>4</v>
       </c>
@@ -30451,10 +28735,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE76">
+        <v>1</v>
       </c>
       <c r="FF76" t="inlineStr">
         <is>
@@ -30466,17 +28748,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH76">
+        <v>1</v>
       </c>
       <c r="FL76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ76" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -30640,10 +28915,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN77">
+        <v>3</v>
       </c>
       <c r="AO77">
         <v>76</v>
@@ -30799,19 +29072,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM77">
+        <v>0</v>
       </c>
       <c r="EN77" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ77" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU77">
@@ -30820,11 +29086,6 @@
       <c r="EW77">
         <v>2</v>
       </c>
-      <c r="EX77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY77">
         <v>4</v>
       </c>
@@ -30843,10 +29104,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE77">
+        <v>1</v>
       </c>
       <c r="FF77" t="inlineStr">
         <is>
@@ -30858,17 +29117,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH77">
+        <v>1</v>
       </c>
       <c r="FL77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -31022,10 +29274,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN78">
+        <v>3</v>
       </c>
       <c r="AO78">
         <v>73</v>
@@ -31179,19 +29429,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM78">
+        <v>0</v>
       </c>
       <c r="EN78" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ78" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU78">
@@ -31200,11 +29443,6 @@
       <c r="EW78">
         <v>2</v>
       </c>
-      <c r="EX78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY78">
         <v>4</v>
       </c>
@@ -31223,10 +29461,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE78">
+        <v>1</v>
       </c>
       <c r="FF78" t="inlineStr">
         <is>
@@ -31238,17 +29474,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH78">
+        <v>1</v>
       </c>
       <c r="FL78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ78" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -31402,10 +29631,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN79">
+        <v>3</v>
       </c>
       <c r="AO79">
         <v>73</v>
@@ -31559,19 +29786,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM79">
+        <v>0</v>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ79" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU79">
@@ -31580,11 +29800,6 @@
       <c r="EW79">
         <v>2</v>
       </c>
-      <c r="EX79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY79">
         <v>4</v>
       </c>
@@ -31603,10 +29818,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE79">
+        <v>1</v>
       </c>
       <c r="FF79" t="inlineStr">
         <is>
@@ -31618,17 +29831,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH79">
+        <v>1</v>
       </c>
       <c r="FL79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ79" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -31782,10 +29988,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN80">
+        <v>3</v>
       </c>
       <c r="AO80">
         <v>73</v>
@@ -31939,19 +30143,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM80">
+        <v>0</v>
       </c>
       <c r="EN80" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ80" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU80">
@@ -31960,11 +30157,6 @@
       <c r="EW80">
         <v>2</v>
       </c>
-      <c r="EX80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY80">
         <v>4</v>
       </c>
@@ -31983,10 +30175,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE80">
+        <v>1</v>
       </c>
       <c r="FF80" t="inlineStr">
         <is>
@@ -31998,17 +30188,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH80">
+        <v>1</v>
       </c>
       <c r="FL80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ80" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -32162,10 +30345,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN81">
+        <v>3</v>
       </c>
       <c r="AO81">
         <v>73</v>
@@ -32319,19 +30500,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM81">
+        <v>0</v>
       </c>
       <c r="EN81" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ81" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU81">
@@ -32340,11 +30514,6 @@
       <c r="EW81">
         <v>2</v>
       </c>
-      <c r="EX81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY81">
         <v>4</v>
       </c>
@@ -32363,10 +30532,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE81">
+        <v>1</v>
       </c>
       <c r="FF81" t="inlineStr">
         <is>
@@ -32378,17 +30545,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH81">
+        <v>1</v>
       </c>
       <c r="FL81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -32542,10 +30702,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN82">
+        <v>3</v>
       </c>
       <c r="AO82">
         <v>73</v>
@@ -32699,19 +30857,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM82">
+        <v>0</v>
       </c>
       <c r="EN82" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ82" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU82">
@@ -32720,11 +30871,6 @@
       <c r="EW82">
         <v>2</v>
       </c>
-      <c r="EX82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY82">
         <v>4</v>
       </c>
@@ -32743,10 +30889,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE82">
+        <v>1</v>
       </c>
       <c r="FF82" t="inlineStr">
         <is>
@@ -32758,17 +30902,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH82">
+        <v>1</v>
       </c>
       <c r="FL82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ82" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -32922,10 +31059,8 @@
           <t>Rational Numbers Word Problems/Problem Solving</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN83">
+        <v>3</v>
       </c>
       <c r="AO83">
         <v>73</v>
@@ -33079,19 +31214,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM83">
+        <v>0</v>
       </c>
       <c r="EN83" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ83" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU83">
@@ -33100,11 +31228,6 @@
       <c r="EW83">
         <v>2</v>
       </c>
-      <c r="EX83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY83">
         <v>4</v>
       </c>
@@ -33123,10 +31246,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE83">
+        <v>1</v>
       </c>
       <c r="FF83" t="inlineStr">
         <is>
@@ -33138,17 +31259,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH83">
+        <v>1</v>
       </c>
       <c r="FL83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -33317,10 +31431,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN84">
+        <v>3</v>
       </c>
       <c r="AO84">
         <v>73</v>
@@ -33482,19 +31594,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM84">
+        <v>0</v>
       </c>
       <c r="EN84" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ84" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU84">
@@ -33503,11 +31608,6 @@
       <c r="EW84">
         <v>2</v>
       </c>
-      <c r="EX84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY84">
         <v>4</v>
       </c>
@@ -33526,10 +31626,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE84">
+        <v>1</v>
       </c>
       <c r="FF84" t="inlineStr">
         <is>
@@ -33541,17 +31639,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH84">
+        <v>1</v>
       </c>
       <c r="FL84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ84" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -33710,10 +31801,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN85">
+        <v>3</v>
       </c>
       <c r="AO85">
         <v>79</v>
@@ -33843,19 +31932,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM85">
+        <v>0</v>
       </c>
       <c r="EN85" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ85" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU85">
@@ -33864,11 +31946,6 @@
       <c r="EW85">
         <v>3</v>
       </c>
-      <c r="EX85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY85">
         <v>4</v>
       </c>
@@ -33887,10 +31964,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE85">
+        <v>1</v>
       </c>
       <c r="FF85" t="inlineStr">
         <is>
@@ -33902,17 +31977,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH85">
+        <v>1</v>
       </c>
       <c r="FL85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ85" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -34071,10 +32139,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN86">
+        <v>3</v>
       </c>
       <c r="AO86">
         <v>79</v>
@@ -34204,19 +32270,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM86">
+        <v>0</v>
       </c>
       <c r="EN86" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ86" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU86">
@@ -34225,11 +32284,6 @@
       <c r="EW86">
         <v>3</v>
       </c>
-      <c r="EX86" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY86">
         <v>4</v>
       </c>
@@ -34248,10 +32302,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE86">
+        <v>1</v>
       </c>
       <c r="FF86" t="inlineStr">
         <is>
@@ -34263,17 +32315,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH86">
+        <v>1</v>
       </c>
       <c r="FL86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -34442,10 +32487,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN87">
+        <v>3</v>
       </c>
       <c r="AO87">
         <v>79</v>
@@ -34580,19 +32623,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM87">
+        <v>0</v>
       </c>
       <c r="EN87" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ87" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU87">
@@ -34601,11 +32637,6 @@
       <c r="EW87">
         <v>3</v>
       </c>
-      <c r="EX87" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY87">
         <v>4</v>
       </c>
@@ -34624,10 +32655,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE87">
+        <v>1</v>
       </c>
       <c r="FF87" t="inlineStr">
         <is>
@@ -34639,17 +32668,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH87">
+        <v>1</v>
       </c>
       <c r="FL87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -34808,10 +32830,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN88">
+        <v>3</v>
       </c>
       <c r="AO88">
         <v>84</v>
@@ -34962,19 +32982,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM88">
+        <v>0</v>
       </c>
       <c r="EN88" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ88" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU88">
@@ -34983,11 +32996,6 @@
       <c r="EW88">
         <v>3</v>
       </c>
-      <c r="EX88" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY88">
         <v>4</v>
       </c>
@@ -35006,10 +33014,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE88">
+        <v>1</v>
       </c>
       <c r="FF88" t="inlineStr">
         <is>
@@ -35021,17 +33027,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH88">
+        <v>1</v>
       </c>
       <c r="FL88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -35190,10 +33189,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN89">
+        <v>3</v>
       </c>
       <c r="AO89">
         <v>84</v>
@@ -35344,19 +33341,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM89">
+        <v>0</v>
       </c>
       <c r="EN89" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ89" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU89">
@@ -35365,11 +33355,6 @@
       <c r="EW89">
         <v>3</v>
       </c>
-      <c r="EX89" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY89">
         <v>4</v>
       </c>
@@ -35388,10 +33373,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE89">
+        <v>1</v>
       </c>
       <c r="FF89" t="inlineStr">
         <is>
@@ -35403,17 +33386,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH89">
+        <v>1</v>
       </c>
       <c r="FL89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ89" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -35582,10 +33558,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN90">
+        <v>3</v>
       </c>
       <c r="AO90">
         <v>84</v>
@@ -35741,19 +33715,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM90">
+        <v>0</v>
       </c>
       <c r="EN90" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ90" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU90">
@@ -35762,11 +33729,6 @@
       <c r="EW90">
         <v>3</v>
       </c>
-      <c r="EX90" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY90">
         <v>4</v>
       </c>
@@ -35785,10 +33747,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE90">
+        <v>1</v>
       </c>
       <c r="FF90" t="inlineStr">
         <is>
@@ -35800,17 +33760,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH90">
+        <v>1</v>
       </c>
       <c r="FL90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ90" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -35974,10 +33927,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN91">
+        <v>3</v>
       </c>
       <c r="AO91">
         <v>84</v>
@@ -36164,19 +34115,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM91">
+        <v>1</v>
       </c>
       <c r="EN91" t="inlineStr">
         <is>
           <t>Fractions knowledge intervention (Face-Off) with conceptual activities</t>
-        </is>
-      </c>
-      <c r="EQ91" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU91">
@@ -36185,11 +34129,6 @@
       <c r="EW91">
         <v>3</v>
       </c>
-      <c r="EX91" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY91">
         <v>4</v>
       </c>
@@ -36208,10 +34147,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE91">
+        <v>1</v>
       </c>
       <c r="FF91" t="inlineStr">
         <is>
@@ -36223,17 +34160,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH91">
+        <v>1</v>
       </c>
       <c r="FL91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ91" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -36397,10 +34327,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN92">
+        <v>3</v>
       </c>
       <c r="AO92">
         <v>84</v>
@@ -36587,19 +34515,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM92">
+        <v>1</v>
       </c>
       <c r="EN92" t="inlineStr">
         <is>
           <t>Fractions knowledge intervention (Face-Off) with conceptual activities</t>
-        </is>
-      </c>
-      <c r="EQ92" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU92">
@@ -36608,11 +34529,6 @@
       <c r="EW92">
         <v>3</v>
       </c>
-      <c r="EX92" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY92">
         <v>4</v>
       </c>
@@ -36631,10 +34547,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE92">
+        <v>1</v>
       </c>
       <c r="FF92" t="inlineStr">
         <is>
@@ -36646,17 +34560,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH92">
+        <v>1</v>
       </c>
       <c r="FL92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ92" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -36835,10 +34742,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN93">
+        <v>3</v>
       </c>
       <c r="AO93">
         <v>84</v>
@@ -37033,19 +34938,12 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="EM93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="EM93">
+        <v>1</v>
       </c>
       <c r="EN93" t="inlineStr">
         <is>
           <t>Fractions knowledge intervention (Face-Off) with conceptual activities</t>
-        </is>
-      </c>
-      <c r="EQ93" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU93">
@@ -37054,11 +34952,6 @@
       <c r="EW93">
         <v>3</v>
       </c>
-      <c r="EX93" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY93">
         <v>4</v>
       </c>
@@ -37077,10 +34970,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE93">
+        <v>1</v>
       </c>
       <c r="FF93" t="inlineStr">
         <is>
@@ -37092,17 +34983,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH93">
+        <v>1</v>
       </c>
       <c r="FL93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ93" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -37271,10 +35155,8 @@
           <t>General Mathematics Achievement</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AN94">
+        <v>1</v>
       </c>
       <c r="AO94">
         <v>107</v>
@@ -37383,19 +35265,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM94">
+        <v>0</v>
       </c>
       <c r="EN94" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ94" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU94">
@@ -37404,11 +35279,6 @@
       <c r="EW94">
         <v>16</v>
       </c>
-      <c r="EX94" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="EY94">
         <v>6</v>
       </c>
@@ -37427,10 +35297,8 @@
           <t>independent</t>
         </is>
       </c>
-      <c r="FE94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="FE94">
+        <v>2</v>
       </c>
       <c r="FF94" t="inlineStr">
         <is>
@@ -37442,19 +35310,12 @@
           <t>school personnel</t>
         </is>
       </c>
-      <c r="FH94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="FH94">
+        <v>2</v>
       </c>
       <c r="FL94" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FQ94" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="FR94" t="b">
@@ -37621,10 +35482,8 @@
           <t>General Mathematics Achievement</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AN95">
+        <v>1</v>
       </c>
       <c r="AO95">
         <v>107</v>
@@ -37733,19 +35592,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM95">
+        <v>0</v>
       </c>
       <c r="EN95" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ95" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU95">
@@ -37754,11 +35606,6 @@
       <c r="EW95">
         <v>17</v>
       </c>
-      <c r="EX95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="EY95">
         <v>6</v>
       </c>
@@ -37777,10 +35624,8 @@
           <t>independent</t>
         </is>
       </c>
-      <c r="FE95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="FE95">
+        <v>2</v>
       </c>
       <c r="FF95" t="inlineStr">
         <is>
@@ -37792,19 +35637,12 @@
           <t>school personnel</t>
         </is>
       </c>
-      <c r="FH95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="FH95">
+        <v>2</v>
       </c>
       <c r="FL95" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FQ95" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="FR95" t="b">
@@ -37986,10 +35824,8 @@
           <t>General Mathematics Achievement</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AN96">
+        <v>1</v>
       </c>
       <c r="AO96">
         <v>110</v>
@@ -38103,19 +35939,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM96">
+        <v>0</v>
       </c>
       <c r="EN96" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ96" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="EU96">
@@ -38124,11 +35953,6 @@
       <c r="EW96">
         <v>18</v>
       </c>
-      <c r="EX96" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="EY96">
         <v>6</v>
       </c>
@@ -38147,34 +35971,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE96" t="inlineStr">
+      <c r="FE96">
+        <v>1</v>
+      </c>
+      <c r="FF96" t="inlineStr">
+        <is>
+          <t>Teachers</t>
+        </is>
+      </c>
+      <c r="FG96" t="inlineStr">
+        <is>
+          <t>school personnel</t>
+        </is>
+      </c>
+      <c r="FH96">
+        <v>2</v>
+      </c>
+      <c r="FL96" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF96" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="FG96" t="inlineStr">
-        <is>
-          <t>school personnel</t>
-        </is>
-      </c>
-      <c r="FH96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="FL96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ96" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="FR96" t="b">
@@ -38326,10 +36141,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN97">
+        <v>3</v>
       </c>
       <c r="AO97">
         <v>28</v>
@@ -38452,19 +36265,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM97">
+        <v>0</v>
       </c>
       <c r="EN97" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ97" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU97">
@@ -38473,11 +36279,6 @@
       <c r="EW97">
         <v>6</v>
       </c>
-      <c r="EX97" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY97">
         <v>5</v>
       </c>
@@ -38496,10 +36297,8 @@
           <t>independent</t>
         </is>
       </c>
-      <c r="FE97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="FE97">
+        <v>2</v>
       </c>
       <c r="FF97" t="inlineStr">
         <is>
@@ -38511,19 +36310,12 @@
           <t>school personnel</t>
         </is>
       </c>
-      <c r="FH97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="FH97">
+        <v>2</v>
       </c>
       <c r="FL97" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FQ97" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR97" t="b">
@@ -38675,10 +36467,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN98">
+        <v>3</v>
       </c>
       <c r="AO98">
         <v>28</v>
@@ -38801,19 +36591,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM98">
+        <v>0</v>
       </c>
       <c r="EN98" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ98" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU98">
@@ -38822,11 +36605,6 @@
       <c r="EW98">
         <v>6</v>
       </c>
-      <c r="EX98" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY98">
         <v>5</v>
       </c>
@@ -38845,34 +36623,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE98" t="inlineStr">
+      <c r="FE98">
+        <v>1</v>
+      </c>
+      <c r="FF98" t="inlineStr">
+        <is>
+          <t>Teachers</t>
+        </is>
+      </c>
+      <c r="FG98" t="inlineStr">
+        <is>
+          <t>school personnel</t>
+        </is>
+      </c>
+      <c r="FH98">
+        <v>2</v>
+      </c>
+      <c r="FL98" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF98" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="FG98" t="inlineStr">
-        <is>
-          <t>school personnel</t>
-        </is>
-      </c>
-      <c r="FH98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="FL98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ98" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR98" t="b">
@@ -39039,10 +36808,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN99">
+        <v>3</v>
       </c>
       <c r="AO99">
         <v>28</v>
@@ -39170,19 +36937,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM99">
+        <v>0</v>
       </c>
       <c r="EN99" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction and any school provided intervention</t>
-        </is>
-      </c>
-      <c r="EQ99" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU99">
@@ -39191,11 +36951,6 @@
       <c r="EW99">
         <v>6</v>
       </c>
-      <c r="EX99" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="EY99">
         <v>5</v>
       </c>
@@ -39214,34 +36969,25 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE99" t="inlineStr">
+      <c r="FE99">
+        <v>1</v>
+      </c>
+      <c r="FF99" t="inlineStr">
+        <is>
+          <t>Teachers</t>
+        </is>
+      </c>
+      <c r="FG99" t="inlineStr">
+        <is>
+          <t>school personnel</t>
+        </is>
+      </c>
+      <c r="FH99">
+        <v>2</v>
+      </c>
+      <c r="FL99" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="FF99" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="FG99" t="inlineStr">
-        <is>
-          <t>school personnel</t>
-        </is>
-      </c>
-      <c r="FH99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="FL99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ99" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="FR99" t="b">
@@ -39398,10 +37144,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN100">
+        <v>3</v>
       </c>
       <c r="AO100">
         <v>44</v>
@@ -39540,19 +37284,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM100">
+        <v>0</v>
       </c>
       <c r="EN100" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ100" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU100">
@@ -39561,11 +37298,6 @@
       <c r="EW100">
         <v>2</v>
       </c>
-      <c r="EX100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY100">
         <v>4.5</v>
       </c>
@@ -39584,10 +37316,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE100">
+        <v>1</v>
       </c>
       <c r="FF100" t="inlineStr">
         <is>
@@ -39599,17 +37329,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH100">
+        <v>1</v>
       </c>
       <c r="FL100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ100" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -39768,10 +37491,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN101">
+        <v>3</v>
       </c>
       <c r="AO101">
         <v>44</v>
@@ -39913,19 +37634,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM101">
+        <v>0</v>
       </c>
       <c r="EN101" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ101" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU101">
@@ -39934,11 +37648,6 @@
       <c r="EW101">
         <v>2</v>
       </c>
-      <c r="EX101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY101">
         <v>4.5</v>
       </c>
@@ -39957,10 +37666,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE101">
+        <v>1</v>
       </c>
       <c r="FF101" t="inlineStr">
         <is>
@@ -39972,17 +37679,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH101">
+        <v>1</v>
       </c>
       <c r="FL101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ101" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -40141,10 +37841,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN102">
+        <v>3</v>
       </c>
       <c r="AO102">
         <v>44</v>
@@ -40286,19 +37984,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM102">
+        <v>0</v>
       </c>
       <c r="EN102" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ102" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU102">
@@ -40307,11 +37998,6 @@
       <c r="EW102">
         <v>2</v>
       </c>
-      <c r="EX102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY102">
         <v>4.5</v>
       </c>
@@ -40330,10 +38016,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE102">
+        <v>1</v>
       </c>
       <c r="FF102" t="inlineStr">
         <is>
@@ -40345,17 +38029,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH102">
+        <v>1</v>
       </c>
       <c r="FL102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ102" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -40514,10 +38191,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN103">
+        <v>3</v>
       </c>
       <c r="AO103">
         <v>44</v>
@@ -40659,19 +38334,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM103">
+        <v>0</v>
       </c>
       <c r="EN103" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ103" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU103">
@@ -40680,11 +38348,6 @@
       <c r="EW103">
         <v>2</v>
       </c>
-      <c r="EX103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY103">
         <v>4.5</v>
       </c>
@@ -40703,10 +38366,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE103">
+        <v>1</v>
       </c>
       <c r="FF103" t="inlineStr">
         <is>
@@ -40718,17 +38379,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH103">
+        <v>1</v>
       </c>
       <c r="FL103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ103" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -40887,10 +38541,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN104">
+        <v>3</v>
       </c>
       <c r="AO104">
         <v>44</v>
@@ -41037,19 +38689,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM104">
+        <v>0</v>
       </c>
       <c r="EN104" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ104" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU104">
@@ -41058,11 +38703,6 @@
       <c r="EW104">
         <v>2</v>
       </c>
-      <c r="EX104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY104">
         <v>4.5</v>
       </c>
@@ -41081,10 +38721,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE104">
+        <v>1</v>
       </c>
       <c r="FF104" t="inlineStr">
         <is>
@@ -41096,17 +38734,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH104">
+        <v>1</v>
       </c>
       <c r="FL104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ104" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -41265,10 +38896,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN105">
+        <v>3</v>
       </c>
       <c r="AO105">
         <v>48</v>
@@ -41410,19 +39039,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM105">
+        <v>0</v>
       </c>
       <c r="EN105" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ105" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU105">
@@ -41431,11 +39053,6 @@
       <c r="EW105">
         <v>2</v>
       </c>
-      <c r="EX105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY105">
         <v>4.5</v>
       </c>
@@ -41454,10 +39071,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE105">
+        <v>1</v>
       </c>
       <c r="FF105" t="inlineStr">
         <is>
@@ -41469,17 +39084,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH105">
+        <v>1</v>
       </c>
       <c r="FL105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ105" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -41638,10 +39246,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN106">
+        <v>3</v>
       </c>
       <c r="AO106">
         <v>48</v>
@@ -41783,19 +39389,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM106">
+        <v>0</v>
       </c>
       <c r="EN106" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ106" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU106">
@@ -41804,11 +39403,6 @@
       <c r="EW106">
         <v>2</v>
       </c>
-      <c r="EX106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY106">
         <v>4.5</v>
       </c>
@@ -41827,10 +39421,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE106">
+        <v>1</v>
       </c>
       <c r="FF106" t="inlineStr">
         <is>
@@ -41842,17 +39434,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH106">
+        <v>1</v>
       </c>
       <c r="FL106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ106" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -42011,10 +39596,8 @@
           <t>Rational Numbers Computation</t>
         </is>
       </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN107">
+        <v>3</v>
       </c>
       <c r="AO107">
         <v>48</v>
@@ -42156,19 +39739,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM107">
+        <v>0</v>
       </c>
       <c r="EN107" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ107" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU107">
@@ -42177,11 +39753,6 @@
       <c r="EW107">
         <v>2</v>
       </c>
-      <c r="EX107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY107">
         <v>4.5</v>
       </c>
@@ -42200,10 +39771,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE107">
+        <v>1</v>
       </c>
       <c r="FF107" t="inlineStr">
         <is>
@@ -42215,17 +39784,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH107">
+        <v>1</v>
       </c>
       <c r="FL107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ107" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -42384,10 +39946,8 @@
           <t>Rational Numbers Knowledge</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN108">
+        <v>3</v>
       </c>
       <c r="AO108">
         <v>48</v>
@@ -42529,19 +40089,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM108">
+        <v>0</v>
       </c>
       <c r="EN108" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ108" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU108">
@@ -42550,11 +40103,6 @@
       <c r="EW108">
         <v>2</v>
       </c>
-      <c r="EX108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY108">
         <v>4.5</v>
       </c>
@@ -42573,10 +40121,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE108">
+        <v>1</v>
       </c>
       <c r="FF108" t="inlineStr">
         <is>
@@ -42588,17 +40134,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH108">
+        <v>1</v>
       </c>
       <c r="FL108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ108" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -42757,10 +40296,8 @@
           <t>Rational Numbers Magnitude Understanding/Relative Magnitude Understanding</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AN109">
+        <v>3</v>
       </c>
       <c r="AO109">
         <v>48</v>
@@ -42910,19 +40447,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="EM109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="EM109">
+        <v>0</v>
       </c>
       <c r="EN109" t="inlineStr">
         <is>
           <t>Business as usual core mathematics instruction</t>
-        </is>
-      </c>
-      <c r="EQ109" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="EU109">
@@ -42931,11 +40461,6 @@
       <c r="EW109">
         <v>2</v>
       </c>
-      <c r="EX109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="EY109">
         <v>4.5</v>
       </c>
@@ -42954,10 +40479,8 @@
           <t>researcher developed</t>
         </is>
       </c>
-      <c r="FE109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FE109">
+        <v>1</v>
       </c>
       <c r="FF109" t="inlineStr">
         <is>
@@ -42969,17 +40492,10 @@
           <t>research staff</t>
         </is>
       </c>
-      <c r="FH109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="FH109">
+        <v>1</v>
       </c>
       <c r="FL109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="FQ109" t="inlineStr">
         <is>
           <t>1</t>
         </is>
